--- a/Tools/Luban/DataTables/Datas/CozyYard/milestone.xlsx
+++ b/Tools/Luban/DataTables/Datas/CozyYard/milestone.xlsx
@@ -30,7 +30,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -41,6 +41,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D9E1F2"/>
         <bgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -62,9 +68,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -432,11 +441,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="25" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
@@ -502,111 +511,125 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
           <t>##</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>名称</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>描述</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>条件类型</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>条件目标ID</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>条件数量</t>
         </is>
       </c>
-      <c r="H2" s="1" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>奖励类型</t>
         </is>
       </c>
-      <c r="I2" s="1" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>奖励ID</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>奖励数量</t>
         </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>初次播种</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>种下第一棵作物</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>PlantCrop</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Coins</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>50</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>初次收获</t>
+          <t>初次播种</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>收获第一棵作物</t>
+          <t>种下第一棵作物</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>HarvestCrop</t>
+          <t>PlantCrop</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -624,103 +647,103 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>安家落户</t>
+          <t>初次收获</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>建造第一座房屋</t>
+          <t>收获第一棵作物</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>BuildBuilding</t>
+          <t>HarvestCrop</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Expansion</t>
+          <t>Coins</t>
         </is>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>养鸡达人</t>
+          <t>安家落户</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>收养第一只动物</t>
+          <t>建造第一座房屋</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AdoptAnimal</t>
+          <t>BuildBuilding</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>Expansion</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1001</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>初学厨艺</t>
+          <t>养鸡达人</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>制作第一道料理</t>
+          <t>收养第一只动物</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CraftItem</t>
+          <t>AdoptAnimal</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -731,34 +754,34 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Coins</t>
+          <t>Item</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1001</v>
       </c>
       <c r="J7" t="n">
-        <v>80</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>远亲近邻</t>
+          <t>初学厨艺</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>完成第一笔订单</t>
+          <t>制作第一道料理</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FulfillOrder</t>
+          <t>CraftItem</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -776,141 +799,141 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>小有规模</t>
+          <t>远亲近邻</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>建造3座设施</t>
+          <t>完成第一笔订单</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>BuildBuilding</t>
+          <t>FulfillOrder</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Expansion</t>
+          <t>Coins</t>
         </is>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>丰收之秋</t>
+          <t>小有规模</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>收获10次作物</t>
+          <t>建造3座设施</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>HarvestCrop</t>
+          <t>BuildBuilding</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>Expansion</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>3006</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>食谱收藏家</t>
+          <t>丰收之秋</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>解锁5个配方</t>
+          <t>收获10次作物</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>UnlockRecipe</t>
+          <t>HarvestCrop</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
+        <v>10</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>3006</v>
+      </c>
+      <c r="J11" t="n">
         <v>5</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Coins</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>200</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>远近闻名</t>
+          <t>食谱收藏家</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>完成5笔订单</t>
+          <t>解锁5个配方</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FulfillOrder</t>
+          <t>UnlockRecipe</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -921,13 +944,51 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
+          <t>Coins</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="n">
+        <v>10</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>远近闻名</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>完成5笔订单</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>FulfillOrder</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>5</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>RecipeUnlock</t>
         </is>
       </c>
-      <c r="I12" t="n">
+      <c r="I13" t="n">
         <v>3</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J13" t="n">
         <v>1</v>
       </c>
     </row>
